--- a/Documentation/Manual Testing.xlsx
+++ b/Documentation/Manual Testing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30015"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\2026-27\CsapatVizsga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94A485AA-F5E7-4256-AF6F-04B2581A578E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0908905B-5EA5-4085-8145-C031F2A9B2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="227">
   <si>
     <t>Test ID</t>
   </si>
@@ -160,7 +160,7 @@
     <t xml:space="preserve"> Product Modify</t>
   </si>
   <si>
-    <t xml:space="preserve">Using this page, the admins can manage the products(modifying them or creating new ones) without the use of backend programming.  Clicking on a product from the list fills the fields so you can modify the ones you want, or just fill them in and create a new one. </t>
+    <t>Using this page, the admins can modify the products without the use of backend programming.  Clicking on a product from the list fills the fields so you can modify the ones you want.</t>
   </si>
   <si>
     <t>ADMIN-06</t>
@@ -172,7 +172,7 @@
     <t>Products have their own images, you can change them to an other img using this panel.</t>
   </si>
   <si>
-    <t>Every data change is working except the change os img.</t>
+    <t>Every data change is working except the change of img. Uploaded img dosn't appear.</t>
   </si>
   <si>
     <t>Error</t>
@@ -187,6 +187,36 @@
     <t>Admin Panel has an Orders Page where the orders data, such as how many times a user comleted an order or the revenue of the site, can be check to see if the site is doing well enough.</t>
   </si>
   <si>
+    <t>ADMIN-08</t>
+  </si>
+  <si>
+    <t>2026.04.22</t>
+  </si>
+  <si>
+    <t>Creating Products</t>
+  </si>
+  <si>
+    <t>Using the Product Modify in Admin Panel, you can creat new products by filling out the filds.</t>
+  </si>
+  <si>
+    <t>After succesfully filling out the filds correctly, the new product is then stored in db and appears on the list.</t>
+  </si>
+  <si>
+    <t>ADMIN-09</t>
+  </si>
+  <si>
+    <t>2026.04.23</t>
+  </si>
+  <si>
+    <t>Img Upload Works</t>
+  </si>
+  <si>
+    <t>Img upload now works in admin panel.</t>
+  </si>
+  <si>
+    <t>Bug fixed</t>
+  </si>
+  <si>
     <t>CART-01</t>
   </si>
   <si>
@@ -241,7 +271,7 @@
     <t>2026.02.21</t>
   </si>
   <si>
-    <t>Logo url-2</t>
+    <t>Logo url</t>
   </si>
   <si>
     <t xml:space="preserve">When you click on the logo it brings you to the home page, only works when not on home page already </t>
@@ -253,6 +283,45 @@
     <t>H-02</t>
   </si>
   <si>
+    <t>2026.02.22</t>
+  </si>
+  <si>
+    <t>About Url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When you click on the "About" text in the header it brings you to the About page, only works when not on About page already </t>
+  </si>
+  <si>
+    <t>Clicking on the "About" text brings you the About page when not already on it. When used on About page it does nothing.</t>
+  </si>
+  <si>
+    <t>H-03</t>
+  </si>
+  <si>
+    <t>Login Url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When you click on the Login text in the header it brings you to the Login page, only works when not on Login page already </t>
+  </si>
+  <si>
+    <t>Clicking on the "Login" text brings you the Login page when not already on it. When used on Login page it does nothing.</t>
+  </si>
+  <si>
+    <t>H-04</t>
+  </si>
+  <si>
+    <t>Cart url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When you click on the Cart icon in the header it brings you to the Cart page, only works when not on Cart page already </t>
+  </si>
+  <si>
+    <t>Clicking on the Cart icon brings you the Cart page when not already on it. When used on Cart page it does nothing.</t>
+  </si>
+  <si>
+    <t>H-05</t>
+  </si>
+  <si>
     <t>2026.02.23</t>
   </si>
   <si>
@@ -265,45 +334,6 @@
     <t>Clicking on the "Products" text brings you the Products page when not already on it. When used on Products page it does nothing.</t>
   </si>
   <si>
-    <t>H-03</t>
-  </si>
-  <si>
-    <t>2026.02.22</t>
-  </si>
-  <si>
-    <t>Login Url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">When you click on the Login text in the header it brings you to the Login page, only works when not on Login page already </t>
-  </si>
-  <si>
-    <t>Clicking on the "Login" text brings you the Login page when not already on it. When used on Login page it does nothing.</t>
-  </si>
-  <si>
-    <t>H-04</t>
-  </si>
-  <si>
-    <t>Cart url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">When you click on the Cart icon in the header it brings you to the Cart page, only works when not on Cart page already </t>
-  </si>
-  <si>
-    <t>Clicking on the Cart icon brings you the Cart page when not already on it. When used on Cart page it does nothing.</t>
-  </si>
-  <si>
-    <t>H-05</t>
-  </si>
-  <si>
-    <t>About Url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">When you click on the "About" text in the header it brings you to the About page, only works when not on About page already </t>
-  </si>
-  <si>
-    <t>Clicking on the "About" text brings you the About page when not already on it. When used on About page it does nothing.</t>
-  </si>
-  <si>
     <t>HOME-01</t>
   </si>
   <si>
@@ -349,7 +379,7 @@
     <t>2026.03.09</t>
   </si>
   <si>
-    <t>Products Swiper</t>
+    <t>Product Swiper</t>
   </si>
   <si>
     <t>Products scroll onHome Page is replaced with swiper,products can be swiped without a scroll button</t>
@@ -364,39 +394,27 @@
     <t>2026.03.22</t>
   </si>
   <si>
+    <t>Product Information</t>
+  </si>
+  <si>
+    <t>Product images appear next to the other product informations</t>
+  </si>
+  <si>
+    <t>Product's informations appear, but images dont.</t>
+  </si>
+  <si>
+    <t>HOME-06</t>
+  </si>
+  <si>
+    <t>2026.03.25</t>
+  </si>
+  <si>
     <t>Product Images</t>
   </si>
   <si>
-    <t>Product images appear next to the other product informations</t>
-  </si>
-  <si>
-    <t>Products informations appear, but images dont</t>
-  </si>
-  <si>
-    <t>HOME-06</t>
-  </si>
-  <si>
-    <t>2026.03.25</t>
-  </si>
-  <si>
-    <t>All informations appear as they should</t>
-  </si>
-  <si>
-    <t>HOME-07</t>
-  </si>
-  <si>
-    <t>2026.03.30</t>
-  </si>
-  <si>
-    <t>Product images are loaded from database</t>
-  </si>
-  <si>
     <t>Product image's appearance fixed</t>
   </si>
   <si>
-    <t>Bug fixed</t>
-  </si>
-  <si>
     <t>LOGIN-01</t>
   </si>
   <si>
@@ -571,7 +589,7 @@
     <t>Username cannot be the same as someone elses</t>
   </si>
   <si>
-    <t>If that username is already used, then you get a network error</t>
+    <t>If that username is already used, then you get a network error insteasd of an error message.</t>
   </si>
   <si>
     <t>SIGNUP-04</t>
@@ -610,13 +628,16 @@
     <t>Button does nothing when spaces are empty or filled out in a wrong way, creates your account when filled out correctly then dropps you back to Login Page</t>
   </si>
   <si>
+    <t>SIGNUP-07</t>
+  </si>
+  <si>
     <t>Login Link</t>
   </si>
   <si>
     <t>Clickin on the text below the Register button in the Register Page, brings you back to the Login Page</t>
   </si>
   <si>
-    <t>SIGNUP-07</t>
+    <t>SIGNUP-08</t>
   </si>
   <si>
     <t>2026.04.01</t>
@@ -725,7 +746,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -742,9 +763,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -755,7 +788,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -886,12 +919,124 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -901,8 +1046,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -913,46 +1061,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -972,21 +1081,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1266,1073 +1375,1346 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr defaultColWidth="23.7109375" defaultRowHeight="116.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" style="13" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" style="13" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" style="13"/>
-    <col min="4" max="4" width="44" style="13" customWidth="1"/>
-    <col min="5" max="5" width="37.28515625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="23.7109375" style="13"/>
-    <col min="7" max="7" width="23.7109375" style="9"/>
-    <col min="8" max="8" width="12.7109375" style="16" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="17" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="16" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" style="17" customWidth="1"/>
-    <col min="12" max="16384" width="23.7109375" style="9"/>
+    <col min="1" max="1" width="14.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" style="5"/>
+    <col min="4" max="4" width="44" style="5" customWidth="1"/>
+    <col min="5" max="5" width="37.28515625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="23.7109375" style="5"/>
+    <col min="7" max="7" width="23.7109375" style="4"/>
+    <col min="8" max="8" width="12.7109375" style="7" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" style="8" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" style="8" customWidth="1"/>
+    <col min="12" max="16384" width="23.7109375" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="60.75" customHeight="1" thickBot="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
     </row>
     <row r="2" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
+      <c r="F2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
+      <c r="F3" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="F4" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="12"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="20"/>
     </row>
     <row r="5" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="F5" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="20"/>
     </row>
     <row r="6" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="F6" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="20"/>
     </row>
     <row r="7" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="F7" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="20"/>
     </row>
     <row r="8" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="F8" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="20"/>
     </row>
     <row r="9" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="16" t="s">
         <v>38</v>
       </c>
+      <c r="G9" s="12"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="20"/>
     </row>
     <row r="10" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="F10" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="20"/>
     </row>
     <row r="11" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="13" t="s">
+      <c r="B11" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="C11" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="D11" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="116.25" customHeight="1" thickBot="1">
-      <c r="A12" s="13" t="s">
+      <c r="E11" s="10" t="s">
         <v>46</v>
       </c>
+      <c r="F11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="20"/>
+    </row>
+    <row r="12" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A12" s="16" t="s">
+        <v>47</v>
+      </c>
       <c r="B12" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="C12" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
+      <c r="D12" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="12"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="20"/>
     </row>
     <row r="13" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A13" s="10" t="s">
-        <v>50</v>
+      <c r="A13" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="12" t="s">
+      <c r="C13" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A14" s="13" t="s">
+      <c r="D13" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="E13" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14" spans="1:11" ht="116.25" customHeight="1" thickBot="1">
+      <c r="A14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="14" t="s">
+      <c r="C14" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="D14" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
     </row>
     <row r="15" spans="1:11" ht="116.25" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="B15" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="D15" s="14" t="s">
         <v>62</v>
       </c>
+      <c r="E15" s="15" t="s">
+        <v>63</v>
+      </c>
       <c r="F15" s="13" t="s">
         <v>10</v>
       </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="20"/>
     </row>
     <row r="16" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A16" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="18" t="s">
+      <c r="A16" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="B16" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="F16" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A17" s="13" t="s">
+      <c r="F16" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="12"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A17" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A18" s="13" t="s">
+      <c r="F17" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="12"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A18" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="12"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A19" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="12"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A20" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="12"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="20"/>
+    </row>
+    <row r="21" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A21" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="12"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A22" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="12"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A19" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="18" t="s">
+      <c r="C23" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A24" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A20" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A21" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A22" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22" s="13" t="s">
+      <c r="C24" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="12"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A25" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="20"/>
+    </row>
+    <row r="26" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A26" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G26" s="12"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="20"/>
+    </row>
+    <row r="27" spans="1:11" ht="126" customHeight="1">
+      <c r="A27" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27" s="12"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="20"/>
+    </row>
+    <row r="28" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A28" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="12"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="20"/>
+    </row>
+    <row r="29" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A29" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="12"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="20"/>
+    </row>
+    <row r="30" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A30" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="12"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="20"/>
+    </row>
+    <row r="31" spans="1:11" ht="139.5" customHeight="1">
+      <c r="A31" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="12"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="20"/>
+    </row>
+    <row r="32" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A32" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="12"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="20"/>
+    </row>
+    <row r="33" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A33" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="12"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="20"/>
+    </row>
+    <row r="34" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A34" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="12"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="20"/>
+    </row>
+    <row r="35" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A35" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+    </row>
+    <row r="36" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A36" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="B36" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A23" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A24" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="F24" s="13" t="s">
+      <c r="C36" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="12"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="20"/>
+    </row>
+    <row r="37" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A37" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="12"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="20"/>
+    </row>
+    <row r="38" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A38" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="F38" s="16" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="126" customHeight="1">
-      <c r="A25" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A26" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="E26" s="13" t="s">
+      <c r="G38" s="12"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="20"/>
+    </row>
+    <row r="39" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A39" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G39" s="12"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="20"/>
+    </row>
+    <row r="40" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A40" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="12"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="20"/>
+    </row>
+    <row r="41" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A41" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="12"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="20"/>
+    </row>
+    <row r="42" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A42" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G42" s="12"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="20"/>
+    </row>
+    <row r="43" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A43" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="12"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="20"/>
+    </row>
+    <row r="44" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A44" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="12"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="20"/>
+    </row>
+    <row r="45" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A45" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="12"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="20"/>
+    </row>
+    <row r="46" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A46" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="12"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="19"/>
+      <c r="K46" s="20"/>
+    </row>
+    <row r="47" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A47" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G47" s="12"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="19"/>
+      <c r="K47" s="20"/>
+    </row>
+    <row r="48" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A48" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="12"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="19"/>
+      <c r="K48" s="20"/>
+    </row>
+    <row r="49" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A49" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" s="12"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="19"/>
+      <c r="K49" s="20"/>
+    </row>
+    <row r="50" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A50" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="12"/>
+      <c r="H50" s="19"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="19"/>
+      <c r="K50" s="20"/>
+    </row>
+    <row r="51" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A51" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B51" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="F26" s="13" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A27" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A28" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A29" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="139.5" customHeight="1">
-      <c r="A30" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A31" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A32" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A33" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A34" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-    </row>
-    <row r="35" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A35" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A36" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="B36" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A37" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A38" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A39" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A40" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A41" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A42" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A43" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A44" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A45" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="E45" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A46" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="F46" s="13" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A47" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="E47" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="F47" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="116.25" customHeight="1">
-      <c r="A48" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A49" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="F49" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A50" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="116.25" customHeight="1">
-      <c r="A51" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="C51" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="F51" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="12"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="19"/>
+      <c r="K51" s="20"/>
+    </row>
+    <row r="52" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A52" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="F52" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" s="12"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="20"/>
+    </row>
+    <row r="53" spans="1:11" ht="116.25" customHeight="1">
+      <c r="A53" s="16"/>
+      <c r="B53" s="16"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="19"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="19"/>
+      <c r="K53" s="20"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F54">
-    <sortCondition ref="A2:A54"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F52">
+    <sortCondition ref="A2:A52"/>
   </sortState>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Bug fixed">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Error">
+      <formula>NOT(ISERROR(SEARCH("Error",F1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Bug fixed">
       <formula>NOT(ISERROR(SEARCH("Bug fixed",F1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Error">
-      <formula>NOT(ISERROR(SEARCH("Error",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2342,134 +2724,169 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F88970F9-2B42-4B46-B679-6CEFB7733DA4}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="23" defaultRowHeight="33" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="23" style="6"/>
-    <col min="2" max="2" width="23" style="7"/>
-    <col min="3" max="3" width="23" style="3"/>
-    <col min="4" max="4" width="23" style="6"/>
-    <col min="5" max="5" width="23" style="7"/>
-    <col min="6" max="16384" width="23" style="3"/>
+    <col min="1" max="1" width="23" style="2"/>
+    <col min="2" max="2" width="23" style="3"/>
+    <col min="3" max="3" width="23" style="1"/>
+    <col min="4" max="4" width="23" style="2"/>
+    <col min="5" max="5" width="23" style="3"/>
+    <col min="6" max="16384" width="23" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="33" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B1" s="2" cm="1">
+      <c r="A1" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="27" cm="1">
         <f t="array" ref="B1">MAX(INDEX(IFERROR(VALUE(SUBSTITUTE(Tests!A:A, "ACCOUNT-", "")), 0), 0))</f>
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="E1" s="20">
+      <c r="C1" s="28"/>
+      <c r="D1" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="E1" s="30">
         <f>COUNTIF(Tests!F:F, "Done")</f>
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="33" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B2" s="2" cm="1">
+      <c r="A2" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" s="27" cm="1">
         <f t="array" ref="B2">MAX(INDEX(IFERROR(VALUE(SUBSTITUTE(Tests!A:A, "ADMIN-", "")), 0), 0))</f>
-        <v>7</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="E2" s="20">
+        <v>9</v>
+      </c>
+      <c r="C2" s="28"/>
+      <c r="D2" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="E2" s="30">
         <f>COUNTIF(Tests!F:F, "Error")</f>
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="33" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B3" s="2" cm="1">
+      <c r="A3" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="B3" s="27" cm="1">
         <f t="array" ref="B3">MAX(INDEX(IFERROR(VALUE(SUBSTITUTE(Tests!A:A, "CART-", "")), 0), 0))</f>
         <v>4</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="E3" s="5">
+      <c r="C3" s="28"/>
+      <c r="D3" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E3" s="31">
         <f>COUNTIF(Tests!F:F, "Bug fixed")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="33" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B4" s="2" cm="1">
+      <c r="A4" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="B4" s="27" cm="1">
         <f t="array" ref="B4">MAX(INDEX(IFERROR(VALUE(SUBSTITUTE(Tests!A:A, "H-", "")), 0), 0))</f>
         <v>5</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="C4" s="28"/>
+      <c r="D4" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="E4" s="27">
         <f>E2-E3</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="33" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B5" s="2" cm="1">
+      <c r="A5" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="B5" s="27" cm="1">
         <f t="array" ref="B5">MAX(INDEX(IFERROR(VALUE(SUBSTITUTE(Tests!A:A, "HOME-", "")), 0), 0))</f>
-        <v>7</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="33"/>
     </row>
     <row r="6" spans="1:5" ht="33" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B6" s="2" cm="1">
+      <c r="A6" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="B6" s="27" cm="1">
         <f t="array" ref="B6">MAX(INDEX(IFERROR(VALUE(SUBSTITUTE(Tests!A:A, "LOGIN-", "")), 0), 0))</f>
         <v>4</v>
       </c>
+      <c r="C6" s="28"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="33"/>
     </row>
     <row r="7" spans="1:5" ht="33" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B7" s="2" cm="1">
+      <c r="A7" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="B7" s="27" cm="1">
         <f t="array" ref="B7">MAX(INDEX(IFERROR(VALUE(SUBSTITUTE(Tests!A:A, "ORDER-", "")), 0), 0))</f>
         <v>4</v>
       </c>
+      <c r="C7" s="28"/>
+      <c r="D7" s="32">
+        <f>SUM(B1:B10)</f>
+        <v>51</v>
+      </c>
+      <c r="E7" s="33">
+        <f>SUM(E1:E3)</f>
+        <v>51</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="33" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B8" s="2" cm="1">
+      <c r="A8" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="B8" s="27" cm="1">
         <f t="array" ref="B8">MAX(INDEX(IFERROR(VALUE(SUBSTITUTE(Tests!A:A, "PROD-", "")), 0), 0))</f>
         <v>4</v>
       </c>
+      <c r="C8" s="28"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="33"/>
     </row>
     <row r="9" spans="1:5" ht="33" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B9" s="5" cm="1">
+      <c r="A9" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="B9" s="31" cm="1">
         <f t="array" ref="B9">MAX(INDEX(IFERROR(VALUE(SUBSTITUTE(Tests!A:A, "SIGNUP-", "")), 0), 0))</f>
-        <v>7</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C9" s="28"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="33"/>
     </row>
     <row r="10" spans="1:5" ht="33" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="B10" s="2" cm="1">
+      <c r="A10" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B10" s="27" cm="1">
         <f t="array" ref="B10">MAX(INDEX(IFERROR(VALUE(SUBSTITUTE(Tests!A:A, "THEME-", "")), 0), 0))</f>
         <v>5</v>
       </c>
+      <c r="C10" s="28"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="33"/>
+    </row>
+    <row r="11" spans="1:5" ht="33" customHeight="1">
+      <c r="A11" s="32"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="33"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E4">
